--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487040_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487040_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1336</v>
+        <v>0.5723</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6157</v>
+        <v>2.054</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7493</v>
+        <v>-1.4816</v>
       </c>
       <c r="G2" t="n">
         <v>-1.0993</v>
@@ -610,13 +610,13 @@
         <v>1.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2929</v>
+        <v>-0.587</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3304</v>
+        <v>0.1078</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9624</v>
+        <v>-0.6947</v>
       </c>
       <c r="V2" t="n">
         <v>1.2936</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MARCOS SÁNCHEZ</t>
+          <t>E. MADINABEITIA GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.5337</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8228</v>
+        <v>1.3619</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0984</v>
+        <v>-1.8956</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.2857</v>
+        <v>-2.7614</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6116</v>
+        <v>-0.1324</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.674</v>
+        <v>-2.629</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5848</v>
+        <v>0.6282</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0828</v>
+        <v>1.8577</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6676</v>
+        <v>-1.2295</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7009</v>
+        <v>-3.3896</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6944</v>
+        <v>-1.9901</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0064</v>
+        <v>-1.3995</v>
       </c>
       <c r="P3" t="n">
-        <v>0.965</v>
+        <v>0.193</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>0.965</v>
+        <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4693</v>
+        <v>-0.4868</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.238</v>
+        <v>0.2079</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2313</v>
+        <v>-0.6947</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06560000000000001</v>
+        <v>2.5216</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X3" t="n">
         <v>0.06560000000000001</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. MADINABEITIA GARCIA</t>
+          <t>A. MARCOS SÁNCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.3397</v>
+        <v>-0.5706</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8236</v>
+        <v>-0.7226</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1633</v>
+        <v>0.152</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.7614</v>
+        <v>-1.2857</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1324</v>
+        <v>-0.6116</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.629</v>
+        <v>-0.674</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6282</v>
+        <v>-0.5848</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8577</v>
+        <v>0.0828</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2295</v>
+        <v>-0.6676</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.3896</v>
+        <v>-0.7009</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.9901</v>
+        <v>-0.6944</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3995</v>
+        <v>-0.0064</v>
       </c>
       <c r="P4" t="n">
-        <v>0.193</v>
+        <v>0.965</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1231</v>
+        <v>0.965</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2929</v>
+        <v>-0.3156</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3304</v>
+        <v>-0.1378</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9624</v>
+        <v>-0.1778</v>
       </c>
       <c r="V4" t="n">
-        <v>2.5216</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0.06560000000000001</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5666</v>
+        <v>-1.7361</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3668</v>
+        <v>0.3043</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9334</v>
+        <v>-2.0404</v>
       </c>
       <c r="G5" t="n">
         <v>-1.8392</v>
@@ -844,13 +844,13 @@
         <v>0.579</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4772</v>
+        <v>0.3077</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2168</v>
+        <v>-0.3239</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5906</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>S. LOPEZ RAMOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8284</v>
+        <v>-2.0731</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7748</v>
+        <v>-0.8242</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0536</v>
+        <v>-1.2489</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.107</v>
+        <v>-1.7278</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9002</v>
+        <v>-0.1469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7933</v>
+        <v>-1.5808</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4278</v>
+        <v>-0.6269</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2641</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6919</v>
+        <v>-0.6269</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5348</v>
+        <v>-1.1009</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6361</v>
+        <v>-0.1469</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1014</v>
+        <v>-0.9539</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3511</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1231</v>
+        <v>-0.193</v>
       </c>
       <c r="R6" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3437</v>
+        <v>-0.3454</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6346000000000001</v>
+        <v>-0.0043</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2909</v>
+        <v>-0.3411</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. LOPEZ RAMOS</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2328</v>
+        <v>-2.2389</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9838</v>
+        <v>-1.0782</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2489</v>
+        <v>-1.1607</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7278</v>
+        <v>-1.107</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1469</v>
+        <v>-1.9002</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5808</v>
+        <v>0.7933</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6269</v>
+        <v>0.4278</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.2641</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6269</v>
+        <v>0.6919</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1009</v>
+        <v>-1.5348</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1469</v>
+        <v>-1.6361</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9539</v>
+        <v>0.1014</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.193</v>
+        <v>-2.1231</v>
       </c>
       <c r="R7" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.505</v>
+        <v>-0.0668</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1639</v>
+        <v>0.3312</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3411</v>
+        <v>-0.3979</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2159</v>
+        <v>-3.2625</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0404</v>
+        <v>-1.1406</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1755</v>
+        <v>-2.1219</v>
       </c>
       <c r="G8" t="n">
         <v>-3.1429</v>
@@ -1078,13 +1078,13 @@
         <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1732</v>
+        <v>-0.2198</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3252</v>
+        <v>0.2251</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4984</v>
+        <v>-0.4449</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2859</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1748</v>
+        <v>-5.3249</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1729</v>
+        <v>-2.8144</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0019</v>
+        <v>-2.5105</v>
       </c>
       <c r="G9" t="n">
         <v>-3.6297</v>
@@ -1156,13 +1156,13 @@
         <v>1.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9683</v>
+        <v>-0.1818</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6954</v>
+        <v>0.0539</v>
       </c>
       <c r="U9" t="n">
-        <v>0.273</v>
+        <v>-0.2357</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5484</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.8425</v>
+        <v>-6.429</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7109</v>
+        <v>-2.351</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.1315</v>
+        <v>-4.078</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2192</v>
@@ -1234,13 +1234,13 @@
         <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.5608</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4019</v>
+        <v>-0.042</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5724</v>
+        <v>-0.5189</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4559</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.7364</v>
+        <v>-7.7112</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4819</v>
+        <v>-4.4835</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2545</v>
+        <v>-3.2278</v>
       </c>
       <c r="G11" t="n">
         <v>-7.9509</v>
@@ -1312,13 +1312,13 @@
         <v>0.772</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3187</v>
+        <v>-0.2935</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6861</v>
+        <v>0.3124</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.6058</v>
       </c>
       <c r="V11" t="n">
         <v>1.8842</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-30.795</v>
+        <v>-29.3077</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.1814</v>
+        <v>-9.694300000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-19.6135</v>
+        <v>-19.6134</v>
       </c>
       <c r="G12" t="n">
         <v>-27.7631</v>
@@ -1390,13 +1390,13 @@
         <v>11.5804</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.2371</v>
+        <v>-2.7498</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1986</v>
+        <v>1.6858</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.4353</v>
+        <v>-4.4354</v>
       </c>
       <c r="V12" t="n">
         <v>2.1701</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.1398</v>
+        <v>13.5099</v>
       </c>
       <c r="E13" t="n">
-        <v>10.0655</v>
+        <v>8.863799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>5.0743</v>
+        <v>4.646</v>
       </c>
       <c r="G13" t="n">
         <v>9.293699999999999</v>
@@ -1468,13 +1468,13 @@
         <v>1.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9969</v>
+        <v>1.3669</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1046</v>
+        <v>0.9029</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8923</v>
+        <v>0.464</v>
       </c>
       <c r="V13" t="n">
         <v>1.8842</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.1358</v>
+        <v>6.5485</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1719</v>
+        <v>5.3708</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9639</v>
+        <v>1.1777</v>
       </c>
       <c r="G14" t="n">
         <v>5.8533</v>
@@ -1546,13 +1546,13 @@
         <v>1.5441</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3597</v>
+        <v>0.7724</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5269</v>
+        <v>0.7258</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1673</v>
+        <v>0.0466</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6562</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0238</v>
+        <v>6.4845</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6402</v>
+        <v>4.9406</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3836</v>
+        <v>1.5439</v>
       </c>
       <c r="G15" t="n">
         <v>4.228</v>
@@ -1624,13 +1624,13 @@
         <v>0.965</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5678</v>
+        <v>1.0285</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6372</v>
+        <v>0.9376</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0694</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>1.228</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.7803</v>
+        <v>6.1938</v>
       </c>
       <c r="E16" t="n">
-        <v>3.337</v>
+        <v>3.9378</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4433</v>
+        <v>2.256</v>
       </c>
       <c r="G16" t="n">
         <v>6.4671</v>
@@ -1702,13 +1702,13 @@
         <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4938</v>
+        <v>-0.0803</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8328</v>
+        <v>-0.232</v>
       </c>
       <c r="U16" t="n">
-        <v>0.339</v>
+        <v>0.1517</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2036</v>
+        <v>4.0989</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6888</v>
+        <v>2.2896</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5148</v>
+        <v>1.8092</v>
       </c>
       <c r="G17" t="n">
         <v>3.4485</v>
@@ -1780,13 +1780,13 @@
         <v>1.7371</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3028</v>
+        <v>-0.4075</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7733</v>
+        <v>-0.1725</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5295</v>
+        <v>-0.235</v>
       </c>
       <c r="V17" t="n">
         <v>0.2859</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5534</v>
+        <v>0.6264</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7308</v>
+        <v>0.8309</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1774</v>
+        <v>-0.2045</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5468</v>
@@ -1858,13 +1858,13 @@
         <v>0.579</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2353</v>
+        <v>0.3083</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2512</v>
+        <v>0.3513</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0159</v>
+        <v>-0.043</v>
       </c>
       <c r="V18" t="n">
         <v>0.2859</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3038</v>
+        <v>0.13</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0005</v>
+        <v>-0.2008</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3043</v>
+        <v>0.3308</v>
       </c>
       <c r="G19" t="n">
         <v>1.4247</v>
@@ -1936,13 +1936,13 @@
         <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2651</v>
+        <v>1.0913</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1263</v>
+        <v>0.9261</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1388</v>
+        <v>0.1652</v>
       </c>
       <c r="V19" t="n">
         <v>-1.228</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7498</v>
+        <v>-0.4157</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9912</v>
+        <v>-0.7909</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2414</v>
+        <v>0.3753</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6444</v>
@@ -2014,13 +2014,13 @@
         <v>0.386</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1633</v>
+        <v>0.1709</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.119</v>
+        <v>0.0813</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0443</v>
+        <v>0.0896</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3281</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6337</v>
+        <v>-1.133</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1779</v>
+        <v>-1.6772</v>
       </c>
       <c r="F21" t="n">
         <v>0.5442</v>
@@ -2092,10 +2092,10 @@
         <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4891</v>
+        <v>0.0116</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3278</v>
+        <v>0.1729</v>
       </c>
       <c r="U21" t="n">
         <v>-0.1613</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. CHACON RODRIGUEZ</t>
+          <t>E. SALINERO GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.943</v>
+        <v>-2.2506</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8998</v>
+        <v>-2.4505</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0431</v>
+        <v>0.1999</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2619</v>
+        <v>-0.1062</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.511</v>
+        <v>3.0005</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7729</v>
+        <v>-3.1067</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2013</v>
+        <v>-1.0344</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1903</v>
+        <v>2.7271</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3916</v>
+        <v>-3.7614</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0605</v>
+        <v>0.9281</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3207</v>
+        <v>0.2734</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3813</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.1231</v>
+        <v>0.386</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>0.772</v>
+        <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>1.7602</v>
+        <v>-0.7307</v>
       </c>
       <c r="T22" t="n">
-        <v>1.7939</v>
+        <v>-0.4511</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0337</v>
+        <v>-0.2796</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.842</v>
+        <v>-1.7997</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.842</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. SALINERO GARCIA</t>
+          <t>I. CHACON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.019</v>
+        <v>-2.33</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9512</v>
+        <v>-1.5007</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0678</v>
+        <v>-0.8293</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1062</v>
+        <v>0.2619</v>
       </c>
       <c r="H23" t="n">
-        <v>3.0005</v>
+        <v>-1.511</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.1067</v>
+        <v>1.7729</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0344</v>
+        <v>0.2013</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7271</v>
+        <v>-1.1903</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.7614</v>
+        <v>1.3916</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9281</v>
+        <v>0.0605</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2734</v>
+        <v>-0.3207</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.3813</v>
       </c>
       <c r="P23" t="n">
-        <v>0.386</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4991</v>
+        <v>1.3732</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9518</v>
+        <v>1.1931</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5473</v>
+        <v>0.1801</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7997</v>
+        <v>-1.842</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7997</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>30.795</v>
+        <v>31.4627</v>
       </c>
       <c r="E24" t="n">
-        <v>19.6136</v>
+        <v>19.6134</v>
       </c>
       <c r="F24" t="n">
-        <v>11.1815</v>
+        <v>11.8492</v>
       </c>
       <c r="G24" t="n">
         <v>27.7632</v>
@@ -2317,7 +2317,7 @@
         <v>5.8477</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9649</v>
+        <v>0.9649000000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-11.5803</v>
@@ -2326,13 +2326,13 @@
         <v>12.5455</v>
       </c>
       <c r="S24" t="n">
-        <v>4.236899999999999</v>
+        <v>4.904599999999999</v>
       </c>
       <c r="T24" t="n">
         <v>4.4354</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1986000000000001</v>
+        <v>0.4692000000000002</v>
       </c>
       <c r="V24" t="n">
         <v>-2.17</v>
